--- a/docs/guides/redteam-prod-real-conversations.xlsx
+++ b/docs/guides/redteam-prod-real-conversations.xlsx
@@ -10,7 +10,9 @@
     <sheet name="실제 대화 (dedup)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="요약 통계" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'실제 대화 (dedup)'!$A$1:$U$645</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -61866,6 +61868,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:U645"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -61903,7 +61906,7 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>2026-05-04 02:36:40</t>
+          <t>2026-05-04 02:43:15</t>
         </is>
       </c>
     </row>

--- a/docs/guides/redteam-prod-real-conversations.xlsx
+++ b/docs/guides/redteam-prod-real-conversations.xlsx
@@ -551,7 +551,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Cache Hit</t>
+          <t>검색 수행</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -7105,7 +7105,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -8932,7 +8932,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -9047,7 +9047,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -9266,7 +9266,7 @@
       <c r="C79" s="5" t="inlineStr"/>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -9971,7 +9971,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -10311,7 +10311,7 @@
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
@@ -10507,7 +10507,7 @@
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -10577,7 +10577,7 @@
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
@@ -11089,7 +11089,7 @@
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -11201,7 +11201,7 @@
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -11427,7 +11427,7 @@
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -11546,7 +11546,7 @@
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -11769,7 +11769,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -11988,7 +11988,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -12096,7 +12096,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -12206,7 +12206,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -12538,7 +12538,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -12751,7 +12751,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -12860,7 +12860,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -12962,7 +12962,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -13282,7 +13282,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -13389,7 +13389,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -13606,7 +13606,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -13716,7 +13716,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -13906,7 +13906,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -14012,7 +14012,7 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -14098,7 +14098,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -14317,7 +14317,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -14631,7 +14631,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -14715,7 +14715,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -14910,7 +14910,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -15013,7 +15013,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -15111,7 +15111,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -15220,7 +15220,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -15325,7 +15325,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -15423,7 +15423,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -15520,7 +15520,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -15719,7 +15719,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -15820,7 +15820,7 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -15928,7 +15928,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -16023,7 +16023,7 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -16117,7 +16117,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -16218,7 +16218,7 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -16508,7 +16508,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -16603,7 +16603,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -16701,7 +16701,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -16984,7 +16984,7 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -17197,7 +17197,7 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -17303,7 +17303,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -17526,7 +17526,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -17633,7 +17633,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -17739,7 +17739,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -17847,7 +17847,7 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -17956,7 +17956,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -18066,7 +18066,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -18178,7 +18178,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -18293,7 +18293,7 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -18397,7 +18397,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -18503,7 +18503,7 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -18613,7 +18613,7 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -18723,7 +18723,7 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -18837,7 +18837,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -18941,7 +18941,7 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -19046,7 +19046,7 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -19155,7 +19155,7 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -19372,7 +19372,7 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -19581,7 +19581,7 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -19683,7 +19683,7 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -19791,7 +19791,7 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -20002,7 +20002,7 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -20095,7 +20095,7 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -20188,7 +20188,7 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -20292,7 +20292,7 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -20398,7 +20398,7 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -20490,7 +20490,7 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -20591,7 +20591,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -20684,7 +20684,7 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -20779,7 +20779,7 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -20975,7 +20975,7 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -21072,7 +21072,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -21263,7 +21263,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -21359,7 +21359,7 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -21463,7 +21463,7 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -21562,7 +21562,7 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -21660,7 +21660,7 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -21734,7 +21734,7 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -21915,7 +21915,7 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -22023,7 +22023,7 @@
       </c>
       <c r="D202" s="7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E202" s="7" t="inlineStr">
@@ -22138,7 +22138,7 @@
       </c>
       <c r="D203" s="7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E203" s="7" t="inlineStr">
@@ -22241,7 +22241,7 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -22311,7 +22311,7 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -22381,7 +22381,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -22464,7 +22464,7 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
@@ -22534,7 +22534,7 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -22612,7 +22612,7 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -22682,7 +22682,7 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -22775,7 +22775,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -22988,7 +22988,7 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
@@ -23096,7 +23096,7 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -23200,7 +23200,7 @@
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
@@ -23302,7 +23302,7 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -23414,7 +23414,7 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -23519,7 +23519,7 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -23628,7 +23628,7 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -23728,7 +23728,7 @@
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -23836,7 +23836,7 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
@@ -23940,7 +23940,7 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -24043,7 +24043,7 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -24144,7 +24144,7 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -24247,7 +24247,7 @@
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
@@ -24358,7 +24358,7 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -24463,7 +24463,7 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -24567,7 +24567,7 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -24680,7 +24680,7 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -24782,7 +24782,7 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -24878,7 +24878,7 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -24980,7 +24980,7 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -25088,7 +25088,7 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -25196,7 +25196,7 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -25308,7 +25308,7 @@
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -25410,7 +25410,7 @@
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
@@ -25628,7 +25628,7 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -25738,7 +25738,7 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -25850,7 +25850,7 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -25958,7 +25958,7 @@
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -26065,7 +26065,7 @@
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -26175,7 +26175,7 @@
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -26281,7 +26281,7 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
@@ -26384,7 +26384,7 @@
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
@@ -26493,7 +26493,7 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
@@ -26593,7 +26593,7 @@
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
@@ -26702,7 +26702,7 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
@@ -26809,7 +26809,7 @@
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
@@ -26918,7 +26918,7 @@
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -27026,7 +27026,7 @@
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
@@ -27131,7 +27131,7 @@
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
@@ -27243,7 +27243,7 @@
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
@@ -27351,7 +27351,7 @@
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
@@ -27456,7 +27456,7 @@
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
@@ -27559,7 +27559,7 @@
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
@@ -27670,7 +27670,7 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
@@ -27778,7 +27778,7 @@
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
@@ -27888,7 +27888,7 @@
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
@@ -27998,7 +27998,7 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
@@ -28109,7 +28109,7 @@
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
@@ -28214,7 +28214,7 @@
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
@@ -28323,7 +28323,7 @@
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
@@ -28432,7 +28432,7 @@
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
@@ -28534,7 +28534,7 @@
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
@@ -28640,7 +28640,7 @@
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
@@ -28744,7 +28744,7 @@
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
@@ -28849,7 +28849,7 @@
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -28950,7 +28950,7 @@
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
@@ -29048,7 +29048,7 @@
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
@@ -29150,7 +29150,7 @@
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
@@ -29248,7 +29248,7 @@
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
@@ -29342,7 +29342,7 @@
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
@@ -29438,7 +29438,7 @@
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
@@ -29619,7 +29619,7 @@
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
@@ -29715,7 +29715,7 @@
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
@@ -29811,7 +29811,7 @@
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
@@ -29905,7 +29905,7 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
@@ -30000,7 +30000,7 @@
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
@@ -30095,7 +30095,7 @@
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
@@ -30191,7 +30191,7 @@
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
@@ -30285,7 +30285,7 @@
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
@@ -30383,7 +30383,7 @@
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
@@ -30478,7 +30478,7 @@
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
@@ -30574,7 +30574,7 @@
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
@@ -30670,7 +30670,7 @@
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
@@ -30765,7 +30765,7 @@
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
@@ -30861,7 +30861,7 @@
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
@@ -30963,7 +30963,7 @@
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
@@ -31058,7 +31058,7 @@
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
@@ -31162,7 +31162,7 @@
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
@@ -31261,7 +31261,7 @@
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
@@ -31366,7 +31366,7 @@
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
@@ -31463,7 +31463,7 @@
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
@@ -31556,7 +31556,7 @@
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
@@ -31650,7 +31650,7 @@
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
@@ -31746,7 +31746,7 @@
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
@@ -31855,7 +31855,7 @@
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
@@ -31953,7 +31953,7 @@
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
@@ -32062,7 +32062,7 @@
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
@@ -32160,7 +32160,7 @@
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
@@ -32255,7 +32255,7 @@
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
@@ -32367,7 +32367,7 @@
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
@@ -32472,7 +32472,7 @@
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
@@ -32573,7 +32573,7 @@
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
@@ -32679,7 +32679,7 @@
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
@@ -32782,7 +32782,7 @@
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
@@ -32879,7 +32879,7 @@
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
@@ -32979,7 +32979,7 @@
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
@@ -33083,7 +33083,7 @@
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
@@ -33181,7 +33181,7 @@
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
@@ -33291,7 +33291,7 @@
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
@@ -33395,7 +33395,7 @@
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
@@ -33470,7 +33470,7 @@
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
@@ -33576,7 +33576,7 @@
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
@@ -33685,7 +33685,7 @@
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
@@ -33796,7 +33796,7 @@
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
@@ -33904,7 +33904,7 @@
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
@@ -34015,7 +34015,7 @@
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
@@ -34123,7 +34123,7 @@
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr">
@@ -34211,7 +34211,7 @@
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
@@ -34320,7 +34320,7 @@
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
@@ -34398,7 +34398,7 @@
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
@@ -34502,7 +34502,7 @@
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
@@ -34612,7 +34612,7 @@
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
@@ -34694,7 +34694,7 @@
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
@@ -34806,7 +34806,7 @@
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
@@ -34913,7 +34913,7 @@
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
@@ -35021,7 +35021,7 @@
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
@@ -35121,7 +35121,7 @@
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
@@ -35232,7 +35232,7 @@
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
@@ -35337,7 +35337,7 @@
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
@@ -35424,7 +35424,7 @@
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
@@ -35514,7 +35514,7 @@
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
@@ -35617,7 +35617,7 @@
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
@@ -35721,7 +35721,7 @@
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
@@ -35824,7 +35824,7 @@
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr">
@@ -35897,7 +35897,7 @@
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E339" s="2" t="inlineStr">
@@ -36001,7 +36001,7 @@
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr">
@@ -36107,7 +36107,7 @@
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E341" s="2" t="inlineStr">
@@ -36218,7 +36218,7 @@
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
@@ -36324,7 +36324,7 @@
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr">
@@ -36424,7 +36424,7 @@
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
@@ -36523,7 +36523,7 @@
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
@@ -36623,7 +36623,7 @@
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr">
@@ -36717,7 +36717,7 @@
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr">
@@ -36807,7 +36807,7 @@
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
@@ -36913,7 +36913,7 @@
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
@@ -37010,7 +37010,7 @@
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
@@ -37108,7 +37108,7 @@
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr">
@@ -37202,7 +37202,7 @@
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
@@ -37305,7 +37305,7 @@
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
@@ -37396,7 +37396,7 @@
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr">
@@ -37490,7 +37490,7 @@
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
@@ -37588,7 +37588,7 @@
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
@@ -37687,7 +37687,7 @@
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
@@ -37785,7 +37785,7 @@
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
@@ -37863,7 +37863,7 @@
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
@@ -37963,7 +37963,7 @@
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
@@ -38038,7 +38038,7 @@
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
@@ -38132,7 +38132,7 @@
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
@@ -38234,7 +38234,7 @@
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
@@ -38310,7 +38310,7 @@
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
@@ -38418,7 +38418,7 @@
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
@@ -38527,7 +38527,7 @@
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
@@ -38634,7 +38634,7 @@
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
@@ -38743,7 +38743,7 @@
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
@@ -38839,7 +38839,7 @@
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr">
@@ -38944,7 +38944,7 @@
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
@@ -39053,7 +39053,7 @@
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr">
@@ -39163,7 +39163,7 @@
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
@@ -39269,7 +39269,7 @@
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr">
@@ -39372,7 +39372,7 @@
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
@@ -39475,7 +39475,7 @@
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr">
@@ -39580,7 +39580,7 @@
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
@@ -39689,7 +39689,7 @@
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
@@ -39794,7 +39794,7 @@
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
@@ -39899,7 +39899,7 @@
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
@@ -40007,7 +40007,7 @@
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
@@ -40116,7 +40116,7 @@
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
@@ -40224,7 +40224,7 @@
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
@@ -40332,7 +40332,7 @@
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr">
@@ -40444,7 +40444,7 @@
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
@@ -40555,7 +40555,7 @@
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
@@ -40660,7 +40660,7 @@
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
@@ -40761,7 +40761,7 @@
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
@@ -40865,7 +40865,7 @@
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
@@ -40966,7 +40966,7 @@
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
@@ -41073,7 +41073,7 @@
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
@@ -41182,7 +41182,7 @@
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
@@ -41288,7 +41288,7 @@
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr">
@@ -41391,7 +41391,7 @@
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr">
@@ -41494,7 +41494,7 @@
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
@@ -41594,7 +41594,7 @@
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
@@ -41684,7 +41684,7 @@
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr">
@@ -41782,7 +41782,7 @@
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr">
@@ -41877,7 +41877,7 @@
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr">
@@ -41973,7 +41973,7 @@
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr">
@@ -42071,7 +42071,7 @@
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
@@ -42169,7 +42169,7 @@
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
@@ -42262,7 +42262,7 @@
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
@@ -42358,7 +42358,7 @@
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
@@ -42449,7 +42449,7 @@
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
@@ -42548,7 +42548,7 @@
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
@@ -42639,7 +42639,7 @@
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
@@ -42737,7 +42737,7 @@
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
@@ -42833,7 +42833,7 @@
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
@@ -42933,7 +42933,7 @@
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
@@ -43003,7 +43003,7 @@
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
@@ -43097,7 +43097,7 @@
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
@@ -43194,7 +43194,7 @@
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
@@ -43264,7 +43264,7 @@
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
@@ -43334,7 +43334,7 @@
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
@@ -43404,7 +43404,7 @@
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
@@ -43474,7 +43474,7 @@
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
@@ -43544,7 +43544,7 @@
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
@@ -43614,7 +43614,7 @@
       </c>
       <c r="D418" s="6" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E418" s="6" t="inlineStr">
@@ -43698,7 +43698,7 @@
       </c>
       <c r="D419" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E419" s="8" t="inlineStr">
@@ -43772,7 +43772,7 @@
       </c>
       <c r="D420" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E420" s="8" t="inlineStr">
@@ -43846,7 +43846,7 @@
       </c>
       <c r="D421" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E421" s="8" t="inlineStr">
@@ -43923,7 +43923,7 @@
       </c>
       <c r="D422" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E422" s="8" t="inlineStr">
@@ -43999,7 +43999,7 @@
       </c>
       <c r="D423" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E423" s="8" t="inlineStr">
@@ -44073,7 +44073,7 @@
       </c>
       <c r="D424" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E424" s="8" t="inlineStr">
@@ -44149,7 +44149,7 @@
       </c>
       <c r="D425" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E425" s="8" t="inlineStr">
@@ -44222,7 +44222,7 @@
       </c>
       <c r="D426" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E426" s="8" t="inlineStr">
@@ -44330,7 +44330,7 @@
       </c>
       <c r="D427" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E427" s="8" t="inlineStr">
@@ -44403,7 +44403,7 @@
       </c>
       <c r="D428" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E428" s="8" t="inlineStr">
@@ -44476,7 +44476,7 @@
       </c>
       <c r="D429" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E429" s="8" t="inlineStr">
@@ -44551,7 +44551,7 @@
       </c>
       <c r="D430" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E430" s="8" t="inlineStr">
@@ -44626,7 +44626,7 @@
       </c>
       <c r="D431" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E431" s="8" t="inlineStr">
@@ -44700,7 +44700,7 @@
       </c>
       <c r="D432" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E432" s="8" t="inlineStr">
@@ -44776,7 +44776,7 @@
       </c>
       <c r="D433" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E433" s="8" t="inlineStr">
@@ -44885,7 +44885,7 @@
       </c>
       <c r="D434" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E434" s="8" t="inlineStr">
@@ -44960,7 +44960,7 @@
       </c>
       <c r="D435" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E435" s="8" t="inlineStr">
@@ -45033,7 +45033,7 @@
       </c>
       <c r="D436" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E436" s="8" t="inlineStr">
@@ -45140,7 +45140,7 @@
       </c>
       <c r="D437" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E437" s="8" t="inlineStr">
@@ -45217,7 +45217,7 @@
       </c>
       <c r="D438" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E438" s="8" t="inlineStr">
@@ -45328,7 +45328,7 @@
       </c>
       <c r="D439" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E439" s="8" t="inlineStr">
@@ -45426,7 +45426,7 @@
       </c>
       <c r="D440" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E440" s="8" t="inlineStr">
@@ -45498,7 +45498,7 @@
       </c>
       <c r="D441" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E441" s="8" t="inlineStr">
@@ -45571,7 +45571,7 @@
       </c>
       <c r="D442" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E442" s="8" t="inlineStr">
@@ -45675,7 +45675,7 @@
       </c>
       <c r="D443" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E443" s="8" t="inlineStr">
@@ -45746,7 +45746,7 @@
       </c>
       <c r="D444" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E444" s="8" t="inlineStr">
@@ -45822,7 +45822,7 @@
       </c>
       <c r="D445" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E445" s="8" t="inlineStr">
@@ -45934,7 +45934,7 @@
       </c>
       <c r="D446" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E446" s="8" t="inlineStr">
@@ -46010,7 +46010,7 @@
       </c>
       <c r="D447" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E447" s="8" t="inlineStr">
@@ -46085,7 +46085,7 @@
       </c>
       <c r="D448" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E448" s="8" t="inlineStr">
@@ -46156,7 +46156,7 @@
       </c>
       <c r="D449" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E449" s="8" t="inlineStr">
@@ -46228,7 +46228,7 @@
       </c>
       <c r="D450" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E450" s="8" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="D451" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E451" s="8" t="inlineStr">
@@ -46370,7 +46370,7 @@
       </c>
       <c r="D452" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E452" s="8" t="inlineStr">
@@ -46442,7 +46442,7 @@
       </c>
       <c r="D453" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E453" s="8" t="inlineStr">
@@ -46513,7 +46513,7 @@
       </c>
       <c r="D454" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E454" s="8" t="inlineStr">
@@ -46607,7 +46607,7 @@
       </c>
       <c r="D455" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E455" s="8" t="inlineStr">
@@ -46678,7 +46678,7 @@
       </c>
       <c r="D456" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E456" s="8" t="inlineStr">
@@ -46776,7 +46776,7 @@
       </c>
       <c r="D457" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E457" s="8" t="inlineStr">
@@ -46847,7 +46847,7 @@
       </c>
       <c r="D458" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E458" s="8" t="inlineStr">
@@ -46942,7 +46942,7 @@
       </c>
       <c r="D459" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E459" s="8" t="inlineStr">
@@ -47013,7 +47013,7 @@
       </c>
       <c r="D460" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E460" s="8" t="inlineStr">
@@ -47085,7 +47085,7 @@
       </c>
       <c r="D461" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E461" s="8" t="inlineStr">
@@ -47156,7 +47156,7 @@
       </c>
       <c r="D462" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E462" s="8" t="inlineStr">
@@ -47227,7 +47227,7 @@
       </c>
       <c r="D463" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E463" s="8" t="inlineStr">
@@ -47298,7 +47298,7 @@
       </c>
       <c r="D464" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E464" s="8" t="inlineStr">
@@ -47369,7 +47369,7 @@
       </c>
       <c r="D465" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E465" s="8" t="inlineStr">
@@ -47440,7 +47440,7 @@
       </c>
       <c r="D466" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E466" s="8" t="inlineStr">
@@ -47543,7 +47543,7 @@
       </c>
       <c r="D467" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E467" s="8" t="inlineStr">
@@ -47614,7 +47614,7 @@
       </c>
       <c r="D468" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E468" s="8" t="inlineStr">
@@ -47712,7 +47712,7 @@
       </c>
       <c r="D469" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E469" s="8" t="inlineStr">
@@ -47790,7 +47790,7 @@
       </c>
       <c r="D470" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E470" s="8" t="inlineStr">
@@ -47898,7 +47898,7 @@
       </c>
       <c r="D471" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E471" s="8" t="inlineStr">
@@ -48007,7 +48007,7 @@
       </c>
       <c r="D472" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E472" s="8" t="inlineStr">
@@ -48084,7 +48084,7 @@
       </c>
       <c r="D473" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E473" s="8" t="inlineStr">
@@ -48195,7 +48195,7 @@
       </c>
       <c r="D474" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E474" s="8" t="inlineStr">
@@ -48305,7 +48305,7 @@
       </c>
       <c r="D475" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E475" s="8" t="inlineStr">
@@ -48420,7 +48420,7 @@
       </c>
       <c r="D476" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E476" s="8" t="inlineStr">
@@ -48494,7 +48494,7 @@
       </c>
       <c r="D477" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E477" s="8" t="inlineStr">
@@ -48573,7 +48573,7 @@
       </c>
       <c r="D478" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E478" s="8" t="inlineStr">
@@ -48651,7 +48651,7 @@
       </c>
       <c r="D479" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E479" s="8" t="inlineStr">
@@ -48759,7 +48759,7 @@
       </c>
       <c r="D480" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E480" s="8" t="inlineStr">
@@ -48872,7 +48872,7 @@
       </c>
       <c r="D481" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E481" s="8" t="inlineStr">
@@ -48986,7 +48986,7 @@
       </c>
       <c r="D482" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E482" s="8" t="inlineStr">
@@ -49090,7 +49090,7 @@
       </c>
       <c r="D483" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E483" s="8" t="inlineStr">
@@ -49163,7 +49163,7 @@
       </c>
       <c r="D484" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E484" s="8" t="inlineStr">
@@ -49242,7 +49242,7 @@
       </c>
       <c r="D485" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E485" s="8" t="inlineStr">
@@ -49352,7 +49352,7 @@
       </c>
       <c r="D486" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E486" s="8" t="inlineStr">
@@ -49425,7 +49425,7 @@
       </c>
       <c r="D487" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E487" s="8" t="inlineStr">
@@ -49500,7 +49500,7 @@
       </c>
       <c r="D488" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E488" s="8" t="inlineStr">
@@ -49610,7 +49610,7 @@
       </c>
       <c r="D489" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E489" s="8" t="inlineStr">
@@ -49722,7 +49722,7 @@
       </c>
       <c r="D490" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E490" s="8" t="inlineStr">
@@ -49827,7 +49827,7 @@
       </c>
       <c r="D491" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E491" s="8" t="inlineStr">
@@ -49927,7 +49927,7 @@
       </c>
       <c r="D492" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E492" s="8" t="inlineStr">
@@ -50029,7 +50029,7 @@
       </c>
       <c r="D493" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E493" s="8" t="inlineStr">
@@ -50132,7 +50132,7 @@
       </c>
       <c r="D494" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E494" s="8" t="inlineStr">
@@ -50231,7 +50231,7 @@
       </c>
       <c r="D495" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E495" s="8" t="inlineStr">
@@ -50337,7 +50337,7 @@
       </c>
       <c r="D496" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E496" s="8" t="inlineStr">
@@ -50409,7 +50409,7 @@
       </c>
       <c r="D497" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E497" s="8" t="inlineStr">
@@ -50485,7 +50485,7 @@
       </c>
       <c r="D498" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E498" s="8" t="inlineStr">
@@ -50560,7 +50560,7 @@
       </c>
       <c r="D499" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E499" s="8" t="inlineStr">
@@ -50631,7 +50631,7 @@
       </c>
       <c r="D500" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E500" s="8" t="inlineStr">
@@ -50727,7 +50727,7 @@
       </c>
       <c r="D501" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E501" s="8" t="inlineStr">
@@ -50798,7 +50798,7 @@
       </c>
       <c r="D502" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E502" s="8" t="inlineStr">
@@ -50892,7 +50892,7 @@
       </c>
       <c r="D503" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E503" s="8" t="inlineStr">
@@ -50963,7 +50963,7 @@
       </c>
       <c r="D504" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E504" s="8" t="inlineStr">
@@ -51034,7 +51034,7 @@
       </c>
       <c r="D505" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E505" s="8" t="inlineStr">
@@ -51131,7 +51131,7 @@
       </c>
       <c r="D506" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E506" s="8" t="inlineStr">
@@ -51202,7 +51202,7 @@
       </c>
       <c r="D507" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E507" s="8" t="inlineStr">
@@ -51298,7 +51298,7 @@
       </c>
       <c r="D508" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E508" s="8" t="inlineStr">
@@ -51369,7 +51369,7 @@
       </c>
       <c r="D509" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E509" s="8" t="inlineStr">
@@ -51470,7 +51470,7 @@
       </c>
       <c r="D510" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E510" s="8" t="inlineStr">
@@ -51541,7 +51541,7 @@
       </c>
       <c r="D511" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E511" s="8" t="inlineStr">
@@ -51652,7 +51652,7 @@
       </c>
       <c r="D512" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E512" s="8" t="inlineStr">
@@ -51753,7 +51753,7 @@
       </c>
       <c r="D513" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E513" s="8" t="inlineStr">
@@ -51824,7 +51824,7 @@
       </c>
       <c r="D514" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E514" s="8" t="inlineStr">
@@ -51922,7 +51922,7 @@
       </c>
       <c r="D515" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E515" s="8" t="inlineStr">
@@ -51996,7 +51996,7 @@
       </c>
       <c r="D516" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E516" s="8" t="inlineStr">
@@ -52070,7 +52070,7 @@
       </c>
       <c r="D517" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E517" s="8" t="inlineStr">
@@ -52141,7 +52141,7 @@
       </c>
       <c r="D518" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E518" s="8" t="inlineStr">
@@ -52241,7 +52241,7 @@
       </c>
       <c r="D519" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E519" s="8" t="inlineStr">
@@ -52312,7 +52312,7 @@
       </c>
       <c r="D520" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E520" s="9" t="inlineStr">
@@ -52401,7 +52401,7 @@
       </c>
       <c r="D521" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E521" s="2" t="inlineStr">
@@ -52494,7 +52494,7 @@
       </c>
       <c r="D522" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E522" s="6" t="inlineStr">
@@ -52601,7 +52601,7 @@
       </c>
       <c r="D523" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E523" s="2" t="inlineStr">
@@ -52714,7 +52714,7 @@
       </c>
       <c r="D524" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E524" s="2" t="inlineStr">
@@ -52827,7 +52827,7 @@
       </c>
       <c r="D525" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E525" s="2" t="inlineStr">
@@ -52931,7 +52931,7 @@
       </c>
       <c r="D526" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E526" s="2" t="inlineStr">
@@ -53040,7 +53040,7 @@
       </c>
       <c r="D527" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E527" s="2" t="inlineStr">
@@ -53149,7 +53149,7 @@
       </c>
       <c r="D528" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E528" s="2" t="inlineStr">
@@ -53237,7 +53237,7 @@
       </c>
       <c r="D529" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E529" s="2" t="inlineStr">
@@ -53319,7 +53319,7 @@
       </c>
       <c r="D530" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E530" s="2" t="inlineStr">
@@ -53433,7 +53433,7 @@
       </c>
       <c r="D531" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E531" s="2" t="inlineStr">
@@ -53533,7 +53533,7 @@
       </c>
       <c r="D532" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E532" s="2" t="inlineStr">
@@ -53637,7 +53637,7 @@
       </c>
       <c r="D533" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E533" s="2" t="inlineStr">
@@ -53741,7 +53741,7 @@
       </c>
       <c r="D534" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E534" s="2" t="inlineStr">
@@ -53850,7 +53850,7 @@
       </c>
       <c r="D535" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E535" s="2" t="inlineStr">
@@ -53957,7 +53957,7 @@
       </c>
       <c r="D536" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E536" s="2" t="inlineStr">
@@ -54068,7 +54068,7 @@
       </c>
       <c r="D537" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E537" s="2" t="inlineStr">
@@ -54152,7 +54152,7 @@
       </c>
       <c r="D538" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E538" s="2" t="inlineStr">
@@ -54239,7 +54239,7 @@
       </c>
       <c r="D539" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E539" s="2" t="inlineStr">
@@ -54352,7 +54352,7 @@
       </c>
       <c r="D540" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E540" s="2" t="inlineStr">
@@ -54457,7 +54457,7 @@
       </c>
       <c r="D541" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E541" s="2" t="inlineStr">
@@ -54562,7 +54562,7 @@
       </c>
       <c r="D542" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E542" s="2" t="inlineStr">
@@ -54666,7 +54666,7 @@
       </c>
       <c r="D543" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E543" s="2" t="inlineStr">
@@ -54751,7 +54751,7 @@
       </c>
       <c r="D544" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E544" s="2" t="inlineStr">
@@ -54852,7 +54852,7 @@
       </c>
       <c r="D545" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E545" s="2" t="inlineStr">
@@ -54960,7 +54960,7 @@
       </c>
       <c r="D546" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E546" s="2" t="inlineStr">
@@ -55068,7 +55068,7 @@
       </c>
       <c r="D547" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E547" s="2" t="inlineStr">
@@ -55171,7 +55171,7 @@
       </c>
       <c r="D548" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E548" s="2" t="inlineStr">
@@ -55241,7 +55241,7 @@
       </c>
       <c r="D549" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E549" s="2" t="inlineStr">
@@ -55349,7 +55349,7 @@
       </c>
       <c r="D550" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E550" s="2" t="inlineStr">
@@ -55455,7 +55455,7 @@
       </c>
       <c r="D551" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E551" s="2" t="inlineStr">
@@ -55567,7 +55567,7 @@
       </c>
       <c r="D552" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E552" s="2" t="inlineStr">
@@ -55671,7 +55671,7 @@
       </c>
       <c r="D553" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E553" s="2" t="inlineStr">
@@ -55776,7 +55776,7 @@
       </c>
       <c r="D554" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E554" s="2" t="inlineStr">
@@ -55880,7 +55880,7 @@
       </c>
       <c r="D555" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E555" s="2" t="inlineStr">
@@ -55989,7 +55989,7 @@
       </c>
       <c r="D556" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E556" s="2" t="inlineStr">
@@ -56094,7 +56094,7 @@
       </c>
       <c r="D557" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E557" s="2" t="inlineStr">
@@ -56201,7 +56201,7 @@
       </c>
       <c r="D558" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E558" s="2" t="inlineStr">
@@ -56307,7 +56307,7 @@
       </c>
       <c r="D559" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E559" s="2" t="inlineStr">
@@ -56418,7 +56418,7 @@
       </c>
       <c r="D560" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E560" s="2" t="inlineStr">
@@ -56521,7 +56521,7 @@
       </c>
       <c r="D561" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E561" s="2" t="inlineStr">
@@ -56633,7 +56633,7 @@
       </c>
       <c r="D562" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E562" s="2" t="inlineStr">
@@ -56740,7 +56740,7 @@
       </c>
       <c r="D563" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E563" s="2" t="inlineStr">
@@ -56858,7 +56858,7 @@
       </c>
       <c r="D564" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E564" s="2" t="inlineStr">
@@ -56966,7 +56966,7 @@
       </c>
       <c r="D565" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E565" s="2" t="inlineStr">
@@ -57074,7 +57074,7 @@
       </c>
       <c r="D566" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E566" s="2" t="inlineStr">
@@ -57186,7 +57186,7 @@
       </c>
       <c r="D567" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E567" s="2" t="inlineStr">
@@ -57292,7 +57292,7 @@
       </c>
       <c r="D568" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E568" s="2" t="inlineStr">
@@ -57398,7 +57398,7 @@
       </c>
       <c r="D569" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E569" s="2" t="inlineStr">
@@ -57499,7 +57499,7 @@
       </c>
       <c r="D570" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E570" s="2" t="inlineStr">
@@ -57605,7 +57605,7 @@
       </c>
       <c r="D571" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E571" s="2" t="inlineStr">
@@ -57709,7 +57709,7 @@
       </c>
       <c r="D572" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E572" s="2" t="inlineStr">
@@ -57813,7 +57813,7 @@
       </c>
       <c r="D573" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E573" s="2" t="inlineStr">
@@ -57916,7 +57916,7 @@
       </c>
       <c r="D574" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E574" s="2" t="inlineStr">
@@ -58017,7 +58017,7 @@
       </c>
       <c r="D575" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E575" s="2" t="inlineStr">
@@ -58128,7 +58128,7 @@
       </c>
       <c r="D576" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E576" s="2" t="inlineStr">
@@ -58236,7 +58236,7 @@
       </c>
       <c r="D577" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E577" s="2" t="inlineStr">
@@ -58346,7 +58346,7 @@
       </c>
       <c r="D578" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E578" s="2" t="inlineStr">
@@ -58448,7 +58448,7 @@
       </c>
       <c r="D579" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E579" s="2" t="inlineStr">
@@ -58549,7 +58549,7 @@
       </c>
       <c r="D580" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E580" s="2" t="inlineStr">
@@ -58656,7 +58656,7 @@
       </c>
       <c r="D581" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E581" s="2" t="inlineStr">
@@ -58739,7 +58739,7 @@
       </c>
       <c r="D582" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E582" s="2" t="inlineStr">
@@ -58846,7 +58846,7 @@
       </c>
       <c r="D583" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E583" s="2" t="inlineStr">
@@ -58949,7 +58949,7 @@
       </c>
       <c r="D584" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E584" s="2" t="inlineStr">
@@ -59052,7 +59052,7 @@
       </c>
       <c r="D585" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E585" s="2" t="inlineStr">
@@ -59156,7 +59156,7 @@
       </c>
       <c r="D586" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E586" s="2" t="inlineStr">
@@ -59264,7 +59264,7 @@
       </c>
       <c r="D587" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E587" s="2" t="inlineStr">
@@ -59368,7 +59368,7 @@
       </c>
       <c r="D588" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E588" s="2" t="inlineStr">
@@ -59473,7 +59473,7 @@
       </c>
       <c r="D589" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E589" s="2" t="inlineStr">
@@ -59575,7 +59575,7 @@
       </c>
       <c r="D590" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E590" s="2" t="inlineStr">
@@ -59676,7 +59676,7 @@
       </c>
       <c r="D591" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E591" s="2" t="inlineStr">
@@ -59779,7 +59779,7 @@
       </c>
       <c r="D592" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E592" s="2" t="inlineStr">
@@ -59887,7 +59887,7 @@
       </c>
       <c r="D593" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E593" s="2" t="inlineStr">
@@ -59994,7 +59994,7 @@
       </c>
       <c r="D594" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E594" s="2" t="inlineStr">
@@ -60100,7 +60100,7 @@
       </c>
       <c r="D595" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E595" s="2" t="inlineStr">
@@ -60209,7 +60209,7 @@
       </c>
       <c r="D596" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E596" s="2" t="inlineStr">
@@ -60314,7 +60314,7 @@
       </c>
       <c r="D597" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E597" s="2" t="inlineStr">
@@ -60415,7 +60415,7 @@
       </c>
       <c r="D598" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E598" s="2" t="inlineStr">
@@ -60517,7 +60517,7 @@
       </c>
       <c r="D599" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E599" s="2" t="inlineStr">
@@ -60617,7 +60617,7 @@
       </c>
       <c r="D600" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E600" s="2" t="inlineStr">
@@ -60719,7 +60719,7 @@
       </c>
       <c r="D601" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E601" s="2" t="inlineStr">
@@ -60821,7 +60821,7 @@
       </c>
       <c r="D602" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E602" s="2" t="inlineStr">
@@ -60926,7 +60926,7 @@
       </c>
       <c r="D603" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E603" s="2" t="inlineStr">
@@ -61030,7 +61030,7 @@
       </c>
       <c r="D604" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E604" s="2" t="inlineStr">
@@ -61133,7 +61133,7 @@
       </c>
       <c r="D605" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E605" s="2" t="inlineStr">
@@ -61239,7 +61239,7 @@
       </c>
       <c r="D606" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E606" s="2" t="inlineStr">
@@ -61352,7 +61352,7 @@
       </c>
       <c r="D607" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E607" s="2" t="inlineStr">
@@ -61460,7 +61460,7 @@
       </c>
       <c r="D608" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E608" s="2" t="inlineStr">
@@ -61569,7 +61569,7 @@
       </c>
       <c r="D609" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E609" s="2" t="inlineStr">
@@ -61670,7 +61670,7 @@
       </c>
       <c r="D610" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E610" s="2" t="inlineStr">
@@ -61773,7 +61773,7 @@
       </c>
       <c r="D611" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E611" s="2" t="inlineStr">
@@ -61876,7 +61876,7 @@
       </c>
       <c r="D612" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E612" s="2" t="inlineStr">
@@ -61987,7 +61987,7 @@
       </c>
       <c r="D613" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E613" s="2" t="inlineStr">
@@ -62096,7 +62096,7 @@
       </c>
       <c r="D614" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E614" s="2" t="inlineStr">
@@ -62198,7 +62198,7 @@
       </c>
       <c r="D615" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E615" s="2" t="inlineStr">
@@ -62302,7 +62302,7 @@
       </c>
       <c r="D616" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E616" s="2" t="inlineStr">
@@ -62412,7 +62412,7 @@
       </c>
       <c r="D617" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E617" s="2" t="inlineStr">
@@ -62517,7 +62517,7 @@
       </c>
       <c r="D618" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E618" s="2" t="inlineStr">
@@ -62625,7 +62625,7 @@
       </c>
       <c r="D619" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E619" s="2" t="inlineStr">
@@ -62729,7 +62729,7 @@
       </c>
       <c r="D620" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E620" s="2" t="inlineStr">
@@ -62835,7 +62835,7 @@
       </c>
       <c r="D621" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E621" s="2" t="inlineStr">
@@ -62940,7 +62940,7 @@
       </c>
       <c r="D622" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E622" s="2" t="inlineStr">
@@ -63048,7 +63048,7 @@
       </c>
       <c r="D623" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E623" s="2" t="inlineStr">
@@ -63154,7 +63154,7 @@
       </c>
       <c r="D624" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E624" s="2" t="inlineStr">
@@ -63224,7 +63224,7 @@
       </c>
       <c r="D625" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E625" s="2" t="inlineStr">
@@ -63294,7 +63294,7 @@
       </c>
       <c r="D626" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E626" s="2" t="inlineStr">
@@ -63406,7 +63406,7 @@
       </c>
       <c r="D627" s="7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E627" s="7" t="inlineStr">
@@ -63495,7 +63495,7 @@
       </c>
       <c r="D628" s="7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E628" s="7" t="inlineStr">
@@ -63586,7 +63586,7 @@
       </c>
       <c r="D629" s="7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E629" s="7" t="inlineStr">
@@ -63679,7 +63679,7 @@
       </c>
       <c r="D630" s="7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E630" s="7" t="inlineStr">
@@ -63768,7 +63768,7 @@
       </c>
       <c r="D631" s="7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E631" s="7" t="inlineStr">
@@ -63863,7 +63863,7 @@
       </c>
       <c r="D632" s="7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E632" s="7" t="inlineStr">
@@ -63956,7 +63956,7 @@
       </c>
       <c r="D633" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E633" s="2" t="inlineStr">
@@ -64061,7 +64061,7 @@
       </c>
       <c r="D634" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E634" s="2" t="inlineStr">
@@ -64149,7 +64149,7 @@
       </c>
       <c r="D635" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E635" s="2" t="inlineStr">
@@ -64238,7 +64238,7 @@
       </c>
       <c r="D636" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E636" s="3" t="inlineStr">
@@ -64329,7 +64329,7 @@
       </c>
       <c r="D637" s="7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E637" s="7" t="inlineStr">
@@ -64417,7 +64417,7 @@
       </c>
       <c r="D638" s="7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E638" s="7" t="inlineStr">
@@ -64507,7 +64507,7 @@
       </c>
       <c r="D639" s="7" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E639" s="7" t="inlineStr">
@@ -64579,7 +64579,7 @@
       </c>
       <c r="D640" s="7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E640" s="7" t="inlineStr">
@@ -64674,7 +64674,7 @@
       </c>
       <c r="D641" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E641" s="4" t="inlineStr">
@@ -64766,7 +64766,7 @@
       </c>
       <c r="D642" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E642" s="4" t="inlineStr">
@@ -64860,7 +64860,7 @@
       </c>
       <c r="D643" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E643" s="6" t="inlineStr">
@@ -64948,7 +64948,7 @@
       </c>
       <c r="D644" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E644" s="2" t="inlineStr">
@@ -65038,7 +65038,7 @@
       </c>
       <c r="D645" s="7" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E645" s="7" t="inlineStr">
@@ -65105,7 +65105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -65132,7 +65132,7 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>2026-05-04 02:51:01</t>
+          <t>2026-05-04 03:18:57</t>
         </is>
       </c>
     </row>
@@ -65173,23 +65173,23 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>Cache Hit 페어</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>118 (18.3%) — search/출처 둘 다 비어있는 페어</t>
-        </is>
+          <t>검색 수행 페어 (Y) — RAG 분석 대상</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>526</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>Cache Miss 페어 (정상 RAG)</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="n">
-        <v>526</v>
+          <t>검색 미수행 페어 (N)</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>118 (18.3%) — SearchEvent/AnswerCitation 미생성</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -65249,115 +65249,119 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Cache Hit 판단 근거</t>
+          <t>"검색 수행" 컬럼 의미</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>backend/src/chat/service.py:157 — cache hit 시 full PersistStage 스킵 → SearchEvent/AnswerCitation 미생성. 둘 다 비어있는 메시지를 cache hit 으로 간주.</t>
+          <t>Y = SearchEvent + AnswerCitation 모두 기록된 정상 RAG 페어 (외부 테스터의 RAG 평가 대상). N = mini-persist 분기로 둘 다 미기록.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr"/>
-      <c r="B15" s="11" t="inlineStr"/>
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>"검색 미수행(N)" 의 두 가지 원인</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>(1) Semantic Cache Hit — backend/src/chat/service.py:157-173. 자주 묻는 인기 질문이 cache_threshold=0.88 으로 매칭되어 search 스킵. (2) META_TERMINATED — line 180-196. 인사/메타 발화 ("안녕", "고마워" 등) 는 RAG 자체가 의미 없어 스킵.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>챗봇별 페어 수</t>
+          <t>주의</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>(많은 순)</t>
+          <t>현재 데이터로는 (1) Cache vs (2) Meta 를 정확히 분리 불가. 둘을 분리하려면 backend 측 SessionMessage.skip_reason ENUM 추가가 필요 (별도 작업).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>전체 검색</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="n">
-        <v>504</v>
-      </c>
+      <c r="A17" s="11" t="inlineStr"/>
+      <c r="B17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>전체 검색 (paragraph 본 가동 후보)</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="n">
-        <v>101</v>
+          <t>챗봇별 페어 수</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>(많은 순)</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">섭리/생애 노정 봇 </t>
+          <t>전체 검색</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
-        <v>15</v>
+        <v>504</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>신학/원리 전문 봇</t>
+          <t>전체 검색 (paragraph 본 가동 후보)</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
-        <v>14</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>말씀선집 우선</t>
+          <t xml:space="preserve">섭리/생애 노정 봇 </t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>소스 A 전용</t>
+          <t>신학/원리 전문 봇</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>선민 대서사시 알리미</t>
+          <t>말씀선집 우선</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>소스 A 전용</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>청킹 PoC: 단락</t>
+          <t>선민 대서사시 알리미</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
@@ -65367,7 +65371,7 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>청킹 PoC: 문장</t>
+          <t>?</t>
         </is>
       </c>
       <c r="B26" s="11" t="n">
@@ -65377,10 +65381,30 @@
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
+          <t>청킹 PoC: 단락</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>청킹 PoC: 문장</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
           <t>통일사상 전문 봇</t>
         </is>
       </c>
-      <c r="B27" s="11" t="n">
+      <c r="B29" s="11" t="n">
         <v>1</v>
       </c>
     </row>
